--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Create-Operation-Output.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Create-Operation-Output.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="224">
   <si>
     <t>Property</t>
   </si>
@@ -486,6 +486,16 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Parameters.meta.tag</t>
   </si>
   <si>
@@ -612,6 +622,9 @@
     <t>The name of the parameter (reference to the operation definition).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Parameters.parameter.value[x]</t>
   </si>
   <si>
@@ -625,24 +638,31 @@
     <t>If the parameter is a data type.</t>
   </si>
   <si>
+    <t>ele-1
+inv-1</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>If parameter is a whole resource</t>
+  </si>
+  <si>
+    <t>If the parameter is a whole resource.</t>
+  </si>
+  <si>
+    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+  </si>
+  <si>
     <t xml:space="preserve">inv-1
 </t>
   </si>
   <si>
-    <t>Parameters.parameter.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>If parameter is a whole resource</t>
-  </si>
-  <si>
-    <t>If the parameter is a whole resource.</t>
-  </si>
-  <si>
-    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+    <t>Entity. Role, or Act</t>
   </si>
   <si>
     <t>Parameters.parameter.part</t>
@@ -1049,7 +1069,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="48.5546875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="22.78515625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2343,24 +2363,24 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2386,13 +2406,13 @@
         <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2418,13 +2438,13 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
@@ -2442,7 +2462,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2451,24 +2471,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2494,13 +2514,13 @@
         <v>125</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2550,7 +2570,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2573,10 +2593,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2599,16 +2619,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2634,13 +2654,13 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>75</v>
@@ -2658,7 +2678,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2681,10 +2701,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2707,13 +2727,13 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2752,7 +2772,7 @@
         <v>75</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
@@ -2762,7 +2782,7 @@
         <v>137</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2771,24 +2791,24 @@
         <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2891,10 +2911,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2964,16 +2984,16 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>111</v>
@@ -2999,14 +3019,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3028,16 +3048,16 @@
         <v>104</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3086,7 +3106,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3104,15 +3124,15 @@
         <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3138,12 +3158,14 @@
         <v>98</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -3192,7 +3214,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
@@ -3215,10 +3237,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3241,13 +3263,13 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3298,7 +3320,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3307,7 +3329,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>96</v>
@@ -3316,15 +3338,15 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3347,16 +3369,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3406,7 +3428,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3415,7 +3437,7 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>75</v>
@@ -3424,15 +3446,15 @@
         <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>75</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3458,13 +3480,13 @@
         <v>75</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3514,7 +3536,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3526,7 +3548,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3537,13 +3559,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -3565,13 +3587,13 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3622,7 +3644,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3631,24 +3653,24 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3751,10 +3773,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3824,16 +3846,16 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>111</v>
@@ -3859,14 +3881,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -3888,16 +3910,16 @@
         <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -3946,7 +3968,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -3964,15 +3986,15 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3998,12 +4020,14 @@
         <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4013,7 +4037,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4052,7 +4076,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>84</v>
@@ -4075,10 +4099,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4101,13 +4125,13 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4158,7 +4182,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4167,7 +4191,7 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>96</v>
@@ -4176,15 +4200,15 @@
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4207,16 +4231,16 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4266,7 +4290,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4284,15 +4308,15 @@
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4318,13 +4342,13 @@
         <v>75</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4374,7 +4398,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4386,7 +4410,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Create-Operation-Output.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Create-Operation-Output.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="218">
   <si>
     <t>Property</t>
   </si>
@@ -486,16 +486,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Parameters.meta.tag</t>
   </si>
   <si>
@@ -622,9 +612,6 @@
     <t>The name of the parameter (reference to the operation definition).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Parameters.parameter.value[x]</t>
   </si>
   <si>
@@ -638,8 +625,8 @@
     <t>If the parameter is a data type.</t>
   </si>
   <si>
-    <t>ele-1
-inv-1</t>
+    <t xml:space="preserve">inv-1
+</t>
   </si>
   <si>
     <t>Parameters.parameter.resource</t>
@@ -656,13 +643,6 @@
   </si>
   <si>
     <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inv-1
-</t>
-  </si>
-  <si>
-    <t>Entity. Role, or Act</t>
   </si>
   <si>
     <t>Parameters.parameter.part</t>
@@ -1069,7 +1049,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="48.5546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="22.78515625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2363,24 +2343,24 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2406,13 +2386,13 @@
         <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2438,31 +2418,31 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2471,24 +2451,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2514,13 +2494,13 @@
         <v>125</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2570,7 +2550,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2593,10 +2573,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2619,16 +2599,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2654,31 +2634,31 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2701,10 +2681,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2727,13 +2707,13 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2772,7 +2752,7 @@
         <v>75</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
@@ -2782,7 +2762,7 @@
         <v>137</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2791,24 +2771,24 @@
         <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2911,10 +2891,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2984,16 +2964,16 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>111</v>
@@ -3019,14 +2999,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3048,16 +3028,16 @@
         <v>104</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3106,7 +3086,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3124,15 +3104,15 @@
         <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3158,14 +3138,12 @@
         <v>98</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -3214,7 +3192,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
@@ -3237,10 +3215,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3263,13 +3241,13 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3320,7 +3298,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3329,7 +3307,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>96</v>
@@ -3338,15 +3316,15 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3369,16 +3347,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3428,7 +3406,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3437,7 +3415,7 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>75</v>
@@ -3446,15 +3424,15 @@
         <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3480,13 +3458,13 @@
         <v>75</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3536,7 +3514,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3548,7 +3526,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3559,13 +3537,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -3587,13 +3565,13 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3644,7 +3622,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3653,24 +3631,24 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3773,10 +3751,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3846,16 +3824,16 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>111</v>
@@ -3881,14 +3859,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -3910,16 +3888,16 @@
         <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -3968,7 +3946,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -3986,15 +3964,15 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4020,14 +3998,12 @@
         <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4037,7 +4013,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4076,7 +4052,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>84</v>
@@ -4099,10 +4075,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4125,13 +4101,13 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4182,7 +4158,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4191,7 +4167,7 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>96</v>
@@ -4200,15 +4176,15 @@
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4231,16 +4207,16 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4290,7 +4266,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4308,15 +4284,15 @@
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4342,13 +4318,13 @@
         <v>75</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4398,7 +4374,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4410,7 +4386,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
